--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 81 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 75 clubs short</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1779,8 +1779,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3128,8 +3128,8 @@
       <c r="V25" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W25" s="9" t="n">
-        <v>3</v>
+      <c r="W25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>5</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4980,8 +4980,8 @@
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6902,8 +6902,8 @@
       <c r="S64" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7308,8 +7308,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9151,8 +9151,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9248,8 +9248,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -10051,7 +10051,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10100,8 +10100,8 @@
       <c r="R97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S97" s="9" t="n">
-        <v>1</v>
+      <c r="S97" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T97" s="9" t="n">
         <v>0</v>
@@ -10647,17 +10647,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -14069,7 +14069,7 @@
         </is>
       </c>
       <c r="P138" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q138" s="10" t="n">
         <v>2</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>1</v>
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T143" s="9" t="n">
         <v>0</v>
@@ -16550,7 +16550,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -16599,8 +16599,8 @@
       <c r="R164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S164" s="9" t="n">
-        <v>1</v>
+      <c r="S164" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T164" s="10" t="n">
         <v>1</v>
@@ -18818,7 +18818,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18917,13 +18917,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -19049,7 +19049,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19148,7 +19148,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -19181,7 +19181,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19280,7 +19280,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -19313,7 +19313,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19346,7 +19346,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19394,7 +19394,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -19775,7 +19775,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 75 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 67 clubs short</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2361,8 +2361,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2537,8 +2537,8 @@
       <c r="S19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4768,8 +4768,8 @@
       <c r="S42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="9" t="n">
-        <v>0</v>
+      <c r="T42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U42" s="9" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>2</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9539,8 +9539,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10685,8 +10685,8 @@
       <c r="S103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11867,8 +11867,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12334,8 +12334,8 @@
       <c r="S120" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
+      <c r="T120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U120" s="9" t="n">
         <v>0</v>
@@ -12476,7 +12476,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -12546,8 +12546,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13446,7 +13446,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13501,8 +13501,8 @@
       <c r="T132" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U132" s="9" t="n">
-        <v>0</v>
+      <c r="U132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V132" s="9" t="n">
         <v>2</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13599,10 +13599,10 @@
         <v>1</v>
       </c>
       <c r="U133" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V133" s="9" t="n">
         <v>3</v>
+      </c>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15241,8 +15241,8 @@
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="9" t="n">
-        <v>1</v>
+      <c r="S150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T150" s="9" t="n">
         <v>0</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15632,8 +15632,8 @@
       <c r="S154" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T154" s="9" t="n">
-        <v>0</v>
+      <c r="T154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U154" s="9" t="n">
         <v>0</v>
@@ -15774,7 +15774,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -15844,8 +15844,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16505,8 +16505,8 @@
       <c r="S163" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T163" s="9" t="n">
-        <v>0</v>
+      <c r="T163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U163" s="9" t="n">
         <v>0</v>
@@ -17099,8 +17099,8 @@
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="9" t="n">
-        <v>2</v>
+      <c r="X169" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X171" s="10" t="n">
         <v>4</v>
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -17687,8 +17687,8 @@
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="9" t="n">
-        <v>0</v>
+      <c r="Z175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -18346,7 +18346,7 @@
         <v>0</v>
       </c>
       <c r="S182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T182" s="10" t="n">
         <v>1</v>
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q183" s="9" t="n">
         <v>0</v>
@@ -18851,7 +18851,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19148,7 +19148,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -19313,7 +19313,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19346,7 +19346,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19379,7 +19379,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19478,7 +19478,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19511,13 +19511,13 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -19676,7 +19676,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -19709,7 +19709,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19775,7 +19775,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -19841,7 +19841,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 67 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2190,11 +2190,11 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Compass Speaks Out</t>
+          <t>Compass Toastmates Connect</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2679,7 +2679,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2749,8 +2749,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3622,8 +3622,8 @@
       <c r="Y30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="n">
-        <v>0</v>
+      <c r="Z30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA30" s="10" t="n">
         <v>1</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4101,14 +4101,14 @@
       <c r="W35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X35" s="9" t="n">
-        <v>0</v>
+      <c r="X35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>4</v>
       </c>
       <c r="W37" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>4</v>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4398,8 +4398,8 @@
       <c r="Y38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="n">
-        <v>0</v>
+      <c r="Z38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA38" s="10" t="n">
         <v>1</v>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4495,8 +4495,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5077,8 +5077,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="9" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6047,8 +6047,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6429,8 +6429,8 @@
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>2</v>
+      <c r="X59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7114,8 +7114,8 @@
       <c r="Y66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z66" s="9" t="n">
-        <v>0</v>
+      <c r="Z66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA66" s="10" t="n">
         <v>1</v>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7599,8 +7599,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7685,19 +7685,19 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="9" t="n">
-        <v>0</v>
+      <c r="X72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7793,8 +7793,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7863,8 +7863,8 @@
       <c r="P74" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q74" s="9" t="n">
-        <v>1</v>
+      <c r="Q74" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8375,8 +8375,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8466,8 +8466,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="9" t="n">
-        <v>1</v>
+      <c r="X80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10606,8 +10606,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11076,8 +11076,8 @@
       <c r="T107" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
+      <c r="U107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V107" s="9" t="n">
         <v>1</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11479,8 +11479,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11547,7 +11547,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13419,8 +13419,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="V137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W137" s="9" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14098,8 +14098,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14389,8 +14389,8 @@
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="9" t="n">
-        <v>0</v>
+      <c r="Z141" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -15553,8 +15553,8 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -15871,7 +15871,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -15929,8 +15929,8 @@
       <c r="U157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="9" t="n">
-        <v>2</v>
+      <c r="V157" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -15941,8 +15941,8 @@
       <c r="Y157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z157" s="9" t="n">
-        <v>0</v>
+      <c r="Z157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA157" s="10" t="n">
         <v>1</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16115,7 +16115,7 @@
         <v>0</v>
       </c>
       <c r="S159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T159" s="9" t="n">
         <v>0</v>
@@ -16135,8 +16135,8 @@
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="9" t="n">
-        <v>0</v>
+      <c r="Z159" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA159" s="10" t="n">
         <v>1</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16232,8 +16232,8 @@
       <c r="Y160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z160" s="9" t="n">
-        <v>0</v>
+      <c r="Z160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA160" s="10" t="n">
         <v>1</v>
@@ -16356,7 +16356,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -16426,8 +16426,8 @@
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="9" t="n">
-        <v>0</v>
+      <c r="Z162" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -16523,8 +16523,8 @@
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -16597,7 +16597,7 @@
         <v>2</v>
       </c>
       <c r="R164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S164" s="10" t="n">
         <v>2</v>
@@ -16982,7 +16982,7 @@
         <v>3</v>
       </c>
       <c r="Q168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" s="9" t="n">
         <v>0</v>
@@ -17085,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="S169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T169" s="9" t="n">
         <v>0</v>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -17396,8 +17396,8 @@
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -17590,8 +17590,8 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -17658,7 +17658,7 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q175" s="9" t="n">
         <v>0</v>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -17978,8 +17978,8 @@
       <c r="Y178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z178" s="9" t="n">
-        <v>0</v>
+      <c r="Z178" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA178" s="10" t="n">
         <v>1</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -18063,11 +18063,11 @@
       <c r="U179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V179" s="9" t="n">
-        <v>0</v>
+      <c r="V179" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X179" s="10" t="n">
         <v>7</v>
@@ -18587,7 +18587,7 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -18657,8 +18657,8 @@
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="9" t="n">
-        <v>0</v>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
@@ -18818,7 +18818,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -18851,7 +18851,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -18884,7 +18884,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -18950,7 +18950,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -18983,7 +18983,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -19049,7 +19049,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19082,7 +19082,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -19115,7 +19115,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19181,7 +19181,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -19247,7 +19247,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19379,7 +19379,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19412,7 +19412,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -19445,7 +19445,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19577,7 +19577,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -19610,7 +19610,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -19643,7 +19643,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19709,7 +19709,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -19742,7 +19742,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -19775,7 +19775,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -19841,7 +19841,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -19874,7 +19874,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -19907,7 +19907,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>5</v>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4289,8 +4289,8 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>3</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7972,8 +7972,8 @@
       <c r="T75" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U75" s="9" t="n">
-        <v>0</v>
+      <c r="U75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V75" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>4</v>
       </c>
       <c r="W77" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X77" s="10" t="n">
         <v>7</v>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9318,8 +9318,8 @@
       <c r="P89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" s="9" t="n">
-        <v>1</v>
+      <c r="Q89" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10200,8 +10200,8 @@
       <c r="S98" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U98" s="9" t="n">
         <v>0</v>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10685,8 +10685,8 @@
       <c r="S103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12046,8 +12046,8 @@
       <c r="T117" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V117" s="9" t="n">
         <v>2</v>
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q120" s="10" t="n">
         <v>2</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>1</v>
@@ -13205,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T129" s="9" t="n">
         <v>0</v>
@@ -13216,8 +13216,8 @@
       <c r="V129" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W129" s="9" t="n">
-        <v>3</v>
+      <c r="W129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>6</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14359,8 +14359,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P141" s="9" t="n">
-        <v>2</v>
+      <c r="P141" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q141" s="10" t="n">
         <v>2</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -14959,8 +14959,8 @@
       <c r="U147" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V147" s="9" t="n">
-        <v>3</v>
+      <c r="V147" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15632,8 +15632,8 @@
       <c r="S154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T154" s="9" t="n">
-        <v>0</v>
+      <c r="T154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U154" s="9" t="n">
         <v>0</v>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-12</v>
+        <v>-7</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
@@ -16891,7 +16891,7 @@
         <v>2</v>
       </c>
       <c r="S167" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T167" s="10" t="n">
         <v>1</v>
@@ -17049,13 +17049,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>1</v>
       </c>
       <c r="V169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
@@ -17146,17 +17146,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L170" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -17243,13 +17243,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -17291,7 +17291,7 @@
         <v>4</v>
       </c>
       <c r="W171" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X171" s="10" t="n">
         <v>4</v>
@@ -17520,7 +17520,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -17534,13 +17534,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
@@ -17563,8 +17563,8 @@
       <c r="P174" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q174" s="9" t="n">
-        <v>1</v>
+      <c r="Q174" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R174" s="9" t="n">
         <v>0</v>
@@ -18243,7 +18243,7 @@
         <v>0</v>
       </c>
       <c r="Q181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>0</v>
@@ -18504,13 +18504,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -18933,8 +18933,8 @@
       <c r="T188" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U188" s="9" t="n">
-        <v>0</v>
+      <c r="U188" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V188" s="9" t="n">
         <v>0</v>
@@ -19274,7 +19274,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -19505,7 +19505,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -19604,7 +19604,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -19637,7 +19637,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19670,7 +19670,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19736,7 +19736,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -19835,7 +19835,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -19901,13 +19901,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -19934,7 +19934,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -19967,7 +19967,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -20099,7 +20099,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -20114,7 +20114,7 @@
         <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -20198,7 +20198,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>

--- a/docs/d/217/inyear.xlsx
+++ b/docs/d/217/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 33 clubs short</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2155,8 +2155,8 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="4" t="n">
         <v>-4</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4342,13 +4342,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>55</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>4</v>
       </c>
       <c r="W38" s="10" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>4</v>
@@ -4760,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -4959,8 +4959,8 @@
       <c r="R44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="9" t="n">
-        <v>1</v>
+      <c r="S44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T44" s="10" t="n">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5156,8 +5156,8 @@
       <c r="S46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U46" s="9" t="n">
         <v>0</v>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6794,7 +6794,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -6805,8 +6805,8 @@
       <c r="S63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>4</v>
       </c>
       <c r="W64" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>6</v>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9219,7 +9219,7 @@
         </is>
       </c>
       <c r="P88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q88" s="9" t="n">
         <v>0</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -10844,10 +10844,10 @@
         <v>19</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13777,8 +13777,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P135" s="9" t="n">
-        <v>3</v>
+      <c r="P135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>4</v>
       </c>
       <c r="W141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X141" s="10" t="n">
         <v>7</v>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14665,8 +14665,8 @@
       <c r="T144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
+      <c r="U144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V144" s="9" t="n">
         <v>2</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q147" s="9" t="n">
         <v>0</v>
@@ -14963,7 +14963,7 @@
         <v>4</v>
       </c>
       <c r="W147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>5</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q151" s="10" t="n">
         <v>2</v>
@@ -15497,13 +15497,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
@@ -15885,13 +15885,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16855,13 +16855,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>7</v>
@@ -18046,7 +18046,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q183" s="9" t="n">
         <v>0</v>
@@ -18490,7 +18490,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -18504,17 +18504,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M184" s="8" t="n">
@@ -18531,7 +18531,7 @@
         </is>
       </c>
       <c r="P184" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q184" s="9" t="n">
         <v>0</v>
@@ -18548,11 +18548,11 @@
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V184" s="9" t="n">
-        <v>3</v>
+      <c r="V184" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W184" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X184" s="9" t="n">
         <v>1</v>
@@ -18604,10 +18604,10 @@
         <v>9</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>1</v>
       </c>
       <c r="U188" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V188" s="9" t="n">
         <v>0</v>
@@ -19142,7 +19142,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -19307,13 +19307,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -19340,7 +19340,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -19439,7 +19439,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -19571,7 +19571,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -19868,13 +19868,13 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
         <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -19934,7 +19934,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -20198,7 +20198,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -20213,7 +20213,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
